--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91544</v>
+        <v>91548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -772,45 +772,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444002</v>
+        <v>127444452</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>91548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>250079</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Postia balsamina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä &amp; Y.C. Dai</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801503</v>
+        <v>801591</v>
       </c>
       <c r="R3" t="n">
-        <v>7178449</v>
+        <v>7178479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,12 +843,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,43 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444452</v>
+        <v>127444002</v>
       </c>
       <c r="B4" t="n">
-        <v>91548</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>250079</v>
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia balsamina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Y.C. Dai</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801591</v>
+        <v>801503</v>
       </c>
       <c r="R4" t="n">
-        <v>7178479</v>
+        <v>7178449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,18 +946,12 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -772,43 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444452</v>
+        <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91548</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>250079</v>
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia balsamina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Y.C. Dai</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801591</v>
+        <v>801503</v>
       </c>
       <c r="R3" t="n">
-        <v>7178479</v>
+        <v>7178449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,18 +845,12 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +869,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444002</v>
+        <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>91548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>250079</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Postia balsamina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä &amp; Y.C. Dai</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801503</v>
+        <v>801591</v>
       </c>
       <c r="R4" t="n">
-        <v>7178449</v>
+        <v>7178479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +940,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>91556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444002</v>
+        <v>127444452</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>91559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>250079</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Postia balsamina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä &amp; Y.C. Dai</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801503</v>
+        <v>801591</v>
       </c>
       <c r="R3" t="n">
-        <v>7178449</v>
+        <v>7178479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,12 +843,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,43 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444452</v>
+        <v>127444002</v>
       </c>
       <c r="B4" t="n">
-        <v>91556</v>
+        <v>91359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>250079</v>
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia balsamina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Y.C. Dai</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801591</v>
+        <v>801503</v>
       </c>
       <c r="R4" t="n">
-        <v>7178479</v>
+        <v>7178449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,18 +946,12 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -973,7 +973,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,43 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444452</v>
+        <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91559</v>
+        <v>91367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>250079</v>
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia balsamina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Y.C. Dai</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801591</v>
+        <v>801503</v>
       </c>
       <c r="R3" t="n">
-        <v>7178479</v>
+        <v>7178449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,18 +845,12 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +869,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444002</v>
+        <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91359</v>
+        <v>91567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>250079</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Postia balsamina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä &amp; Y.C. Dai</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801503</v>
+        <v>801591</v>
       </c>
       <c r="R4" t="n">
-        <v>7178449</v>
+        <v>7178479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +940,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -973,7 +973,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -772,45 +772,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444002</v>
+        <v>127444452</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>250079</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Postia balsamina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä &amp; Y.C. Dai</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801503</v>
+        <v>801591</v>
       </c>
       <c r="R3" t="n">
-        <v>7178449</v>
+        <v>7178479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,12 +843,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,43 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444452</v>
+        <v>127444002</v>
       </c>
       <c r="B4" t="n">
-        <v>91567</v>
+        <v>91368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>250079</v>
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia balsamina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Y.C. Dai</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801591</v>
+        <v>801503</v>
       </c>
       <c r="R4" t="n">
-        <v>7178479</v>
+        <v>7178449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,18 +946,12 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127444452</v>
       </c>
       <c r="B3" t="n">
-        <v>91568</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127444002</v>
       </c>
       <c r="B4" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127444452</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127444002</v>
       </c>
       <c r="B4" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -772,43 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444452</v>
+        <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>250079</v>
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia balsamina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Y.C. Dai</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801591</v>
+        <v>801503</v>
       </c>
       <c r="R3" t="n">
-        <v>7178479</v>
+        <v>7178449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,18 +845,12 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +869,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444002</v>
+        <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>250079</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Postia balsamina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä &amp; Y.C. Dai</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801503</v>
+        <v>801591</v>
       </c>
       <c r="R4" t="n">
-        <v>7178449</v>
+        <v>7178479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +940,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Märklig filur. Tagit kollekt och förhoppningsvis får jag iväg den till någon som kan tänka sig mikra den. Beskrivningen i Poroid Fungi of Europe stämmer dock mycket bra med föreslagen art</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>91722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,14 +974,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1075,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91722</v>
+        <v>91726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91726</v>
+        <v>91731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91738</v>
+        <v>91741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91741</v>
+        <v>91744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91744</v>
+        <v>91751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91758</v>
+        <v>91760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127443987</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91760</v>
+        <v>91769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,14 +796,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,7 +876,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91769</v>
+        <v>91770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91770</v>
+        <v>91773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127444002</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91775</v>
+        <v>91779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127443986</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127444002</v>
+        <v>127443987</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,19 +787,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801503</v>
+        <v>801451</v>
       </c>
       <c r="R3" t="n">
-        <v>7178449</v>
+        <v>7178560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +880,7 @@
         <v>127444452</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>92140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,6 +889,11 @@
       </c>
       <c r="E4" t="n">
         <v>250079</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Krämporing</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -976,107 +985,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>127443987</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57887</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Långgrunden, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>801451</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7178560</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35159-2025 artfynd.xlsx
+++ b/artfynd/A 35159-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127443986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127443987</t>
         </is>
       </c>
     </row>
@@ -984,8 +999,18 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127444452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>